--- a/rules/CORE-000224/positive/01/data/unit-test-coreid-CG0515-positive 1.xlsx
+++ b/rules/CORE-000224/positive/01/data/unit-test-coreid-CG0515-positive 1.xlsx
@@ -1740,12 +1740,12 @@
           <t>Zanomaline High Dose (81 mg)</t>
         </is>
       </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>ZAN_HIGH</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="n"/>
+      <c r="V11" s="4" t="n"/>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>Zanomaline High Dose (81 mg)</t>
+        </is>
+      </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
           <t>UNPLANNED</t>
